--- a/output/浙江/浙江_battle4.xlsx
+++ b/output/浙江/浙江_battle4.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -430,14 +430,14 @@
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="38" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -520,7 +520,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>升迁_省委书记</t>
+          <t>升迁_省长</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -531,12 +531,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>离任浙江省委书记后调任上海市委书记，属平级调动</t>
+          <t>离任浙江省代省长后调任上海市委书记，均为正部级，属平级调动</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>离任浙江省委书记后任上海市委书记，后升任中央政治局常委</t>
+          <t>任浙江省代省长后升任浙江省委书记，属于升迁</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -555,19 +555,19 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>离任浙江省委书记后任上海市委书记，由正部级升至副国级，属升迁</t>
+          <t>习近平离任浙江省代省长后升任浙江省委书记，按规则升任本省省委书记即为升迁</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>李强</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>升迁_省长</t>
+          <t>升迁_省委书记</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -588,12 +588,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>离任浙江省省长后平调任江苏省委书记，行政级别均为正部级</t>
+          <t>离任浙江省委书记后调任重庆市委书记，属平级调动</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>离任浙江省省长后任江苏省委书记，后续晋升至副国级、正国级</t>
+          <t>离任浙江省委书记后任中央政治局委员，属副国级晋升</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -612,69 +612,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>按规则看下一个职务：省长→省委书记是平级，非升迁；后续晋升不算。</t>
+          <t>离任浙江省委书记前已当选中央政治局委员，离任后平调重庆市委书记，未发生新的级别晋升，按规则应为0。</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>车俊</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>本省提拔</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>任浙江省代省长前由新疆维吾尔自治区调任，非省内晋升</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>任浙江省代省长前曾任浙江省委副书记，属本省任职</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>95</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>车俊任代省长前最后职务为浙江省委副书记，属本省省级机构，符合本省提拔定义</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>

--- a/output/浙江/浙江_battle4.xlsx
+++ b/output/浙江/浙江_battle4.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -39,6 +39,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8CCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -54,9 +59,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -430,14 +436,14 @@
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="31" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="29" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -510,7 +516,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>习近平</t>
+          <t>葛洪升</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -531,12 +537,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>离任浙江省代省长后调任上海市委书记，均为正部级，属平级调动</t>
+          <t>离任浙江省省长后任国务院特区办副主任（副部级），非升迁</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>任浙江省代省长后升任浙江省委书记，属于升迁</t>
+          <t>1993年10月离任浙江省长后任国务院特区办副主任</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -546,28 +552,28 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>习近平离任浙江省代省长后升任浙江省委书记，按规则升任本省省委书记即为升迁</t>
+          <t>国务院特区办副主任属同级去向，非升迁</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>袁家军</t>
+          <t>万学远</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -577,23 +583,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>升迁_省委书记</t>
+          <t>本省提拔</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>离任浙江省委书记后调任重庆市委书记，属平级调动</t>
+          <t>由浙江省副省长升任浙江省省长，属省内晋升</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>离任浙江省委书记后任中央政治局委员，属副国级晋升</t>
+          <t>任浙江省副省长前在上海市任职，属跨省调入</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -608,16 +614,576 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
+        <v>88</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>任浙江主官前最近经历为浙江省副省长，属本省提拔</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>习近平</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>升迁_省委书记</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>离任浙江省委书记后任上海市委书记，此时未兼任政治局委员，还是省部级，属于平调</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>离任浙江省委书记后任上海市委书记，后兼政治局常委</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>98</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>只看离任后紧接下一职，时任上海市委书记属平调</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>习近平</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>本省学习</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>履历中在浙江省内无脱产全日制学习记录</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1975-1979年在清华大学全日制学习，地点在北京非浙江</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>96</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>清华在北京，不属浙江，本省学习应为0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>吕祖善</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>升迁_省长</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>离任浙江省省长后任全国人大财经委副主任委员，正部级平调</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2011.08离任浙江省长后任全国人大财经委副主任委员（副国级）</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
         <v>95</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>离任浙江省委书记前已当选中央政治局委员，离任后平调重庆市委书记，未发生新的级别晋升，按规则应为0。</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>全国人大财经委副主任委员属正部级，省长后属平调</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>李强</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>升迁_省长</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>离任浙江省长后任江苏省委书记，同属省部级</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>浙江省长离任后任江苏省委书记，为升任省委书记</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>96</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>省长后直接任省委书记，规则判升迁</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>车俊</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>本省提拔</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>任浙江省代省长前为浙江省委副书记，属省内提拔</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>任浙江代省长前为新疆党委副书记，属跨省调入</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>96</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>任浙江省主官前最近主要经历在新疆，属跨省调入</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>袁家军</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>升迁_省长</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>任浙江省省长后升任浙江省委书记</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>离任浙江省长后任浙江省委书记，仍省部级</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>96</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>同省由省长升任省委书记，规则明确算升迁</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>袁家军</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>本省提拔</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>任浙江省省长前为浙江省委副书记，属本省提拔</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>任浙江副省长前在宁夏任常务副主席，跨省调入</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>96</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>任浙江省主官前紧邻职务为中共浙江省委副书记，属省内提拔</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>郑栅洁</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>bio</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>全日制本科</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>郑栅洁有南京化工学院全日制本科学习经历</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>郑栅洁</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>升迁_省长</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>任浙江省省长后调任安徽省委书记，同级平调</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>离任浙江省省长后任安徽省委书记</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>93</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>省长后直接任省委书记，属升迁</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>升迁_省长</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>L24显示仍任浙江省省长（至今）</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>96</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>现任浙江省省长，离任后去向未发生，应标-1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
